--- a/Agentes/Maria/Sistemas de RH/Relatórios/2026-08/Relatório de Entradas e Saídas por Unidade - 2026-08-14.xlsx
+++ b/Agentes/Maria/Sistemas de RH/Relatórios/2026-08/Relatório de Entradas e Saídas por Unidade - 2026-08-14.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>15/08/2026 07:21:49 BRT</t>
+          <t>15/08/2026 10:31:37 BRT</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="N5" s="9" t="inlineStr">
         <is>
-          <t>Marcações pares (10)</t>
+          <t>FÉRIAS</t>
         </is>
       </c>
     </row>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="N6" s="9" t="inlineStr">
         <is>
-          <t>Marcações pares (10)</t>
+          <t>FÉRIAS</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       <c r="M8" s="7" t="inlineStr"/>
       <c r="N8" s="10" t="inlineStr">
         <is>
-          <t>Sem linha de ponto retornada</t>
+          <t>Sem marcação</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       <c r="M11" s="7" t="inlineStr"/>
       <c r="N11" s="10" t="inlineStr">
         <is>
-          <t>Sem linha de ponto retornada</t>
+          <t>Sem marcação</t>
         </is>
       </c>
     </row>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="N5" s="9" t="inlineStr">
         <is>
-          <t>Marcações pares (10)</t>
+          <t>FÉRIAS</t>
         </is>
       </c>
     </row>
